--- a/Báo cáo Đồ án/Phân công Đồ Án.xlsx
+++ b/Báo cáo Đồ án/Phân công Đồ Án.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\congh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ITU\HK 4\4. Hệ thống quản trị qui trình nghiệp vụ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{957E1E1F-9CB2-4D32-93F7-1B2AF9EE5B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD402C36-ACEA-4735-AAF5-3245F11A31F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31890" yWindow="1095" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Phân Công" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="136">
   <si>
     <t>Rubik đánh giá</t>
   </si>
@@ -419,38 +419,45 @@
     <t>2 + 3 + 4</t>
   </si>
   <si>
-    <t>5 + 6</t>
-  </si>
-  <si>
-    <t>Chương 1: Giới thiệu FPT Long Châu;
+    <t>Chương 4: Phương pháp thực hiện và thu thập dữ liệu; xây dựng bộ câu hỏi định tính/định lượng, biểu mẫu và bảng dữ liệu phục vụ nghiên cứu; chuẩn hóa thuật ngữ sử dụng trong bài.</t>
+  </si>
+  <si>
+    <t>Chương 2: Phân loại 10 quy trình, xây dựng Process Architecture và mô tả các quy trình Management; 
+Chương 3: Mô hình hóa 2 quy trình Management bằng BPMN.</t>
+  </si>
+  <si>
+    <t>Chương 1: Giới thiệu FPT Long Châu; tìm kiếm và tổng hợp thông tin doanh nghiệp, nguồn tài liệu chính thống; 
 Chương 7: Kết luận và hướng phát triển.</t>
   </si>
   <si>
-    <t>Chương 2: Phân loại 10 quy trình, xây dựng Process Architecture; 
-Chương 3: Mô hình hóa 2 quy trình Management bằng BPMN.</t>
-  </si>
-  <si>
-    <t>Chương 4: Phương pháp thực hiện và thu thập dữ liệu; 
-Chương 5: Phân tích quy trình Bán thuốc tại nhà thuốc.</t>
-  </si>
-  <si>
-    <t>Chương 5: Phân tích quy trình Quản lý kho; 
-Chương 6: Đề xuất cải tiến và xây dựng BPMN TO-BE.</t>
-  </si>
-  <si>
-    <t>Chương 3: Mô hình hóa 2 quy trình Core bằng BPMN; 
-hỗ trợ mô tả các quy trình Core ở Chương 2.</t>
-  </si>
-  <si>
-    <t>Chương 3: Mô hình hóa 2 quy trình Support bằng BPMN; 
-hỗ trợ mô tả các quy trình Support ở Chương 2.</t>
+    <t>Chương 2: Mô tả các quy trình Core; 
+Chương 3: Mô hình hóa 2 quy trình Core bằng BPMN; 
+Chương 5: Phân tích quy trình Bán thuốc tại nhà thuốc và xây dựng BPMN TO-BE.</t>
+  </si>
+  <si>
+    <t>Chương 2: Mô tả các quy trình Support; 
+Chương 3: Mô hình hóa 2 quy trình Support bằng BPMN; 
+Chương 5: Phân tích quy trình Quản lý kho và xây dựng BPMN TO-BE.</t>
+  </si>
+  <si>
+    <t>Chương 2: Mô tả 3 quy trình còn lại; 
+Chương 6: Tổng hợp giải pháp cải tiến, so sánh AS-IS và TO-BE theo Time – Cost – Quality.</t>
+  </si>
+  <si>
+    <t>2 + 3 + 4 + 6</t>
+  </si>
+  <si>
+    <t>3 + 4</t>
+  </si>
+  <si>
+    <t>3 + 4 + 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -497,6 +504,13 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -518,7 +532,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -536,14 +550,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -760,69 +780,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8D2E7E-EEF5-4F13-B181-FA7E29886EC2}">
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" style="11" customWidth="1"/>
-    <col min="2" max="2" width="38.140625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="11"/>
+    <col min="1" max="1" width="16" style="10" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A3" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
     <row r="4" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="12" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A6" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -837,10 +857,10 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C13" s="7">
@@ -848,21 +868,21 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>126</v>
+      <c r="C14" s="13" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="7" t="s">
         <v>116</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -870,10 +890,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="7" t="s">
         <v>118</v>
       </c>
       <c r="C16" s="7">
@@ -881,37 +901,42 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>127</v>
+      <c r="C17" s="13" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="7">
-        <v>6</v>
+      <c r="C18" s="13" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="7" t="s">
         <v>124</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
       </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
